--- a/data/raw/sales/Week 33/Audio_Array/Vendor Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 33/Audio_Array/Vendor Sales (SP-API).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="448">
   <si>
     <t>ASIN</t>
   </si>
@@ -133,6 +133,9 @@
     <t>B0BQ7H7418</t>
   </si>
   <si>
+    <t>B0C4YSV3XL</t>
+  </si>
+  <si>
     <t>B0CBC7QMNV</t>
   </si>
   <si>
@@ -274,6 +277,9 @@
     <t>B0FJ8TSQK1</t>
   </si>
   <si>
+    <t>B0FJ8TWCQZ</t>
+  </si>
+  <si>
     <t>B0FJ8W5Y9Q</t>
   </si>
   <si>
@@ -487,6 +493,9 @@
     <t>FBA76597</t>
   </si>
   <si>
+    <t>FBA78206</t>
+  </si>
+  <si>
     <t>FBA78925</t>
   </si>
   <si>
@@ -628,6 +637,9 @@
     <t>FBA79830</t>
   </si>
   <si>
+    <t>FBA79835</t>
+  </si>
+  <si>
     <t>FBA79831</t>
   </si>
   <si>
@@ -844,6 +856,9 @@
     <t>AA-06</t>
   </si>
   <si>
+    <t>AM-W15</t>
+  </si>
+  <si>
     <t>AM-C11X</t>
   </si>
   <si>
@@ -985,6 +1000,9 @@
     <t>GB-03 (AI-12 + AM-C43)</t>
   </si>
   <si>
+    <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
+  </si>
+  <si>
     <t>GB-04 (AM-C45 + AI-06)</t>
   </si>
   <si>
@@ -1198,6 +1216,9 @@
     <t>Mobile Microphone</t>
   </si>
   <si>
+    <t>Wireless Mic with Charging Case</t>
+  </si>
+  <si>
     <t>XLR Dynamic Mic</t>
   </si>
   <si>
@@ -1249,6 +1270,9 @@
     <t>GB-03</t>
   </si>
   <si>
+    <t>PB-06</t>
+  </si>
+  <si>
     <t>GB-04</t>
   </si>
   <si>
@@ -1333,7 +1357,7 @@
     <t>2026-08-09</t>
   </si>
   <si>
-    <t>2026-08-14</t>
+    <t>2026-08-15</t>
   </si>
 </sst>
 </file>
@@ -1691,7 +1715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P119"/>
+  <dimension ref="A1:P121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1749,46 +1773,46 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="F2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H2">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="I2">
-        <v>413640.45</v>
+        <v>483527.85</v>
       </c>
       <c r="J2">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M2" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N2">
         <v>33</v>
       </c>
       <c r="O2" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P2" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1796,19 +1820,19 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E3" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="F3" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -1826,16 +1850,16 @@
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P3" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1843,28 +1867,28 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E4" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="F4" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="H4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I4">
-        <v>33494.12</v>
+        <v>39583.96</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -1873,16 +1897,16 @@
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N4">
         <v>33</v>
       </c>
       <c r="O4" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P4" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1890,19 +1914,19 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E5" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="F5" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1920,16 +1944,16 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N5">
         <v>33</v>
       </c>
       <c r="O5" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P5" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1937,28 +1961,28 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D6" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E6" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="F6" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>6437.28</v>
+        <v>8046.6</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -1967,16 +1991,16 @@
         <v>4</v>
       </c>
       <c r="M6" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N6">
         <v>33</v>
       </c>
       <c r="O6" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P6" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1984,19 +2008,19 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C7" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D7" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E7" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="F7" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H7">
         <v>12</v>
@@ -2014,16 +2038,16 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N7">
         <v>33</v>
       </c>
       <c r="O7" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P7" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2031,19 +2055,19 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D8" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E8" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F8" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -2061,16 +2085,16 @@
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N8">
         <v>33</v>
       </c>
       <c r="O8" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P8" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2078,19 +2102,19 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C9" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D9" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E9" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="F9" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H9">
         <v>8</v>
@@ -2108,16 +2132,16 @@
         <v>2</v>
       </c>
       <c r="M9" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N9">
         <v>33</v>
       </c>
       <c r="O9" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P9" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2125,28 +2149,28 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D10" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E10" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="F10" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I10">
-        <v>16196.62</v>
+        <v>21583.08</v>
       </c>
       <c r="J10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2155,16 +2179,16 @@
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N10">
         <v>33</v>
       </c>
       <c r="O10" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P10" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2172,28 +2196,28 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C11" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D11" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E11" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="F11" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>6918.64</v>
+        <v>13837.28</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -2202,16 +2226,16 @@
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N11">
         <v>33</v>
       </c>
       <c r="O11" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P11" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2219,25 +2243,25 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D12" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E12" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="F12" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H12">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I12">
-        <v>9142.32</v>
+        <v>12189.76</v>
       </c>
       <c r="J12">
         <v>10</v>
@@ -2249,16 +2273,16 @@
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N12">
         <v>33</v>
       </c>
       <c r="O12" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P12" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2266,46 +2290,46 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C13" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D13" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E13" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="F13" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H13">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I13">
-        <v>5327.12</v>
+        <v>6468.65</v>
       </c>
       <c r="J13">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N13">
         <v>33</v>
       </c>
       <c r="O13" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P13" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2313,25 +2337,25 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C14" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D14" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E14" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="F14" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>14112.73</v>
+        <v>16120.36</v>
       </c>
       <c r="J14">
         <v>7</v>
@@ -2340,19 +2364,19 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N14">
         <v>33</v>
       </c>
       <c r="O14" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P14" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2360,19 +2384,19 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C15" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D15" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E15" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="F15" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="H15">
         <v>8</v>
@@ -2381,7 +2405,7 @@
         <v>24350.9</v>
       </c>
       <c r="J15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -2390,16 +2414,16 @@
         <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N15">
         <v>33</v>
       </c>
       <c r="O15" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P15" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2407,19 +2431,19 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C16" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D16" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E16" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="F16" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="H16">
         <v>3</v>
@@ -2437,16 +2461,16 @@
         <v>6</v>
       </c>
       <c r="M16" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N16">
         <v>33</v>
       </c>
       <c r="O16" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P16" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2454,28 +2478,28 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C17" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D17" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E17" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="F17" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H17">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I17">
-        <v>17679.63</v>
+        <v>20005.9</v>
       </c>
       <c r="J17">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -2484,16 +2508,16 @@
         <v>3</v>
       </c>
       <c r="M17" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N17">
         <v>33</v>
       </c>
       <c r="O17" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P17" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2501,19 +2525,19 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C18" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D18" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E18" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="F18" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2531,16 +2555,16 @@
         <v>0</v>
       </c>
       <c r="M18" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N18">
         <v>33</v>
       </c>
       <c r="O18" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P18" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2548,19 +2572,19 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C19" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D19" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E19" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="F19" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -2578,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="M19" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N19">
         <v>33</v>
       </c>
       <c r="O19" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P19" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2595,19 +2619,19 @@
         <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C20" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D20" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E20" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="F20" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -2625,16 +2649,16 @@
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N20">
         <v>33</v>
       </c>
       <c r="O20" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P20" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2642,25 +2666,25 @@
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C21" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D21" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E21" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="F21" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="H21">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I21">
-        <v>42479.97</v>
+        <v>45102.01</v>
       </c>
       <c r="J21">
         <v>38</v>
@@ -2672,16 +2696,16 @@
         <v>5</v>
       </c>
       <c r="M21" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N21">
         <v>33</v>
       </c>
       <c r="O21" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P21" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2689,46 +2713,46 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C22" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D22" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E22" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F22" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="H22">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="I22">
-        <v>546922.96</v>
+        <v>649866.1899999999</v>
       </c>
       <c r="J22">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M22" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N22">
         <v>33</v>
       </c>
       <c r="O22" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P22" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2736,19 +2760,19 @@
         <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C23" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D23" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E23" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F23" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="H23">
         <v>7</v>
@@ -2757,7 +2781,7 @@
         <v>22147.45</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2766,16 +2790,16 @@
         <v>1</v>
       </c>
       <c r="M23" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N23">
         <v>33</v>
       </c>
       <c r="O23" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P23" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2783,25 +2807,25 @@
         <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C24" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D24" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E24" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="F24" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H24">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I24">
-        <v>13293.21</v>
+        <v>15325.41</v>
       </c>
       <c r="J24">
         <v>13</v>
@@ -2813,16 +2837,16 @@
         <v>3</v>
       </c>
       <c r="M24" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N24">
         <v>33</v>
       </c>
       <c r="O24" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P24" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2830,25 +2854,25 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C25" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D25" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E25" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F25" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>5828.82</v>
+        <v>0</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -2860,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N25">
         <v>33</v>
       </c>
       <c r="O25" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P25" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2877,46 +2901,46 @@
         <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C26" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D26" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E26" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="F26" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="H26">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>13973.74</v>
+        <v>5828.82</v>
       </c>
       <c r="J26">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N26">
         <v>33</v>
       </c>
       <c r="O26" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P26" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2924,46 +2948,46 @@
         <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C27" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D27" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E27" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F27" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="H27">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="I27">
-        <v>80367.72</v>
+        <v>15244.08</v>
       </c>
       <c r="J27">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M27" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N27">
         <v>33</v>
       </c>
       <c r="O27" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P27" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2971,46 +2995,46 @@
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C28" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D28" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E28" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="F28" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>95812.62</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M28" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N28">
         <v>33</v>
       </c>
       <c r="O28" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P28" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3018,46 +3042,46 @@
         <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C29" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D29" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E29" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F29" t="s">
         <v>396</v>
       </c>
       <c r="H29">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>17791.51</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N29">
         <v>33</v>
       </c>
       <c r="O29" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P29" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3065,46 +3089,46 @@
         <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C30" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D30" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E30" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="F30" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="H30">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I30">
-        <v>65235.58</v>
+        <v>17791.51</v>
       </c>
       <c r="J30">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N30">
         <v>33</v>
       </c>
       <c r="O30" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P30" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3112,46 +3136,46 @@
         <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C31" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D31" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E31" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="F31" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I31">
-        <v>2567.8</v>
+        <v>74131.34</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M31" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N31">
         <v>33</v>
       </c>
       <c r="O31" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P31" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3159,46 +3183,46 @@
         <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C32" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D32" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E32" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F32" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H32">
         <v>2</v>
       </c>
       <c r="I32">
-        <v>1269.5</v>
+        <v>2567.8</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N32">
         <v>33</v>
       </c>
       <c r="O32" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P32" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3206,46 +3230,46 @@
         <v>47</v>
       </c>
       <c r="B33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C33" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D33" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E33" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="F33" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="H33">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I33">
-        <v>34057.57</v>
+        <v>1904.24</v>
       </c>
       <c r="J33">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N33">
         <v>33</v>
       </c>
       <c r="O33" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P33" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3253,46 +3277,46 @@
         <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C34" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D34" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E34" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F34" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I34">
-        <v>2280.5</v>
+        <v>38064.34</v>
       </c>
       <c r="J34">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M34" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N34">
         <v>33</v>
       </c>
       <c r="O34" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P34" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3300,46 +3324,46 @@
         <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C35" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D35" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E35" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="F35" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>2280.5</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N35">
         <v>33</v>
       </c>
       <c r="O35" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P35" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3347,46 +3371,46 @@
         <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C36" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D36" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E36" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F36" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H36">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>24630.73</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N36">
         <v>33</v>
       </c>
       <c r="O36" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P36" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3394,46 +3418,46 @@
         <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C37" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D37" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E37" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="F37" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H37">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="I37">
-        <v>3404.24</v>
+        <v>32107.89</v>
       </c>
       <c r="J37">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M37" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N37">
         <v>33</v>
       </c>
       <c r="O37" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P37" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3441,46 +3465,46 @@
         <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C38" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D38" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E38" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="F38" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H38">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="I38">
-        <v>410306.21</v>
+        <v>4081.36</v>
       </c>
       <c r="J38">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N38">
         <v>33</v>
       </c>
       <c r="O38" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P38" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3488,46 +3512,46 @@
         <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C39" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D39" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E39" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F39" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
       <c r="H39">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="I39">
-        <v>26092.36</v>
+        <v>460533.34</v>
       </c>
       <c r="J39">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M39" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N39">
         <v>33</v>
       </c>
       <c r="O39" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P39" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3535,46 +3559,46 @@
         <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C40" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D40" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E40" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F40" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="H40">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="I40">
-        <v>39099.98</v>
+        <v>28464.39</v>
       </c>
       <c r="J40">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M40" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N40">
         <v>33</v>
       </c>
       <c r="O40" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P40" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3582,46 +3606,46 @@
         <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C41" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D41" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E41" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F41" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="H41">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="I41">
-        <v>20312.64</v>
+        <v>45400.81</v>
       </c>
       <c r="J41">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M41" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N41">
         <v>33</v>
       </c>
       <c r="O41" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P41" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3629,46 +3653,46 @@
         <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C42" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D42" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E42" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F42" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="H42">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="I42">
-        <v>2860.15</v>
+        <v>23538.9</v>
       </c>
       <c r="J42">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M42" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N42">
         <v>33</v>
       </c>
       <c r="O42" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P42" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3676,25 +3700,25 @@
         <v>57</v>
       </c>
       <c r="B43" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C43" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D43" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E43" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="F43" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="H43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I43">
-        <v>20395.76</v>
+        <v>5720.31</v>
       </c>
       <c r="J43">
         <v>5</v>
@@ -3703,19 +3727,19 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N43">
         <v>33</v>
       </c>
       <c r="O43" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P43" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3723,46 +3747,46 @@
         <v>58</v>
       </c>
       <c r="B44" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C44" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D44" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E44" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F44" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I44">
-        <v>931.36</v>
+        <v>20395.76</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M44" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N44">
         <v>33</v>
       </c>
       <c r="O44" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P44" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3770,28 +3794,28 @@
         <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C45" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D45" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E45" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F45" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>931.36</v>
       </c>
       <c r="J45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -3800,16 +3824,16 @@
         <v>5</v>
       </c>
       <c r="M45" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N45">
         <v>33</v>
       </c>
       <c r="O45" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P45" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3817,19 +3841,19 @@
         <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C46" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D46" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E46" t="s">
         <v>376</v>
       </c>
       <c r="F46" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -3838,25 +3862,25 @@
         <v>0</v>
       </c>
       <c r="J46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M46" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N46">
         <v>33</v>
       </c>
       <c r="O46" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P46" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3864,28 +3888,28 @@
         <v>61</v>
       </c>
       <c r="B47" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C47" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D47" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E47" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="F47" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>5523.72</v>
+        <v>0</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -3894,16 +3918,16 @@
         <v>0</v>
       </c>
       <c r="M47" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N47">
         <v>33</v>
       </c>
       <c r="O47" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P47" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3911,28 +3935,28 @@
         <v>62</v>
       </c>
       <c r="B48" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C48" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D48" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E48" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="F48" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="H48">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I48">
-        <v>38310.16</v>
+        <v>5523.72</v>
       </c>
       <c r="J48">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -3941,16 +3965,16 @@
         <v>0</v>
       </c>
       <c r="M48" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N48">
         <v>33</v>
       </c>
       <c r="O48" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P48" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3958,46 +3982,46 @@
         <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C49" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D49" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E49" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F49" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="H49">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I49">
-        <v>15250.85</v>
+        <v>43783.04</v>
       </c>
       <c r="J49">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N49">
         <v>33</v>
       </c>
       <c r="O49" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P49" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4005,28 +4029,28 @@
         <v>64</v>
       </c>
       <c r="B50" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C50" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D50" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E50" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="F50" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I50">
-        <v>7455.93</v>
+        <v>15250.85</v>
       </c>
       <c r="J50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -4035,16 +4059,16 @@
         <v>0</v>
       </c>
       <c r="M50" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N50">
         <v>33</v>
       </c>
       <c r="O50" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P50" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4052,46 +4076,46 @@
         <v>65</v>
       </c>
       <c r="B51" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C51" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D51" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E51" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="F51" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51">
-        <v>2878.82</v>
+        <v>7455.93</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N51">
         <v>33</v>
       </c>
       <c r="O51" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P51" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4099,46 +4123,46 @@
         <v>66</v>
       </c>
       <c r="B52" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C52" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D52" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E52" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="F52" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52">
-        <v>3050</v>
+        <v>2878.82</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52">
         <v>0</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N52">
         <v>33</v>
       </c>
       <c r="O52" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P52" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4146,28 +4170,28 @@
         <v>67</v>
       </c>
       <c r="B53" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C53" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D53" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E53" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="F53" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H53">
         <v>3</v>
       </c>
       <c r="I53">
-        <v>9531.360000000001</v>
+        <v>9150</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K53">
         <v>0</v>
@@ -4176,16 +4200,16 @@
         <v>0</v>
       </c>
       <c r="M53" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N53">
         <v>33</v>
       </c>
       <c r="O53" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P53" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4193,28 +4217,28 @@
         <v>68</v>
       </c>
       <c r="B54" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C54" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D54" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E54" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="F54" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I54">
-        <v>3218.64</v>
+        <v>19062.72</v>
       </c>
       <c r="J54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K54">
         <v>0</v>
@@ -4223,16 +4247,16 @@
         <v>0</v>
       </c>
       <c r="M54" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N54">
         <v>33</v>
       </c>
       <c r="O54" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P54" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4240,28 +4264,28 @@
         <v>69</v>
       </c>
       <c r="B55" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C55" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D55" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E55" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="F55" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I55">
-        <v>25156.8</v>
+        <v>4827.96</v>
       </c>
       <c r="J55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K55">
         <v>0</v>
@@ -4270,16 +4294,16 @@
         <v>0</v>
       </c>
       <c r="M55" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N55">
         <v>33</v>
       </c>
       <c r="O55" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P55" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4287,28 +4311,28 @@
         <v>70</v>
       </c>
       <c r="B56" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C56" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D56" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E56" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F56" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="H56">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I56">
-        <v>9889.83</v>
+        <v>25156.8</v>
       </c>
       <c r="J56">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -4317,16 +4341,16 @@
         <v>0</v>
       </c>
       <c r="M56" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N56">
         <v>33</v>
       </c>
       <c r="O56" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P56" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4334,28 +4358,28 @@
         <v>71</v>
       </c>
       <c r="B57" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C57" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D57" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E57" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="F57" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="H57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I57">
-        <v>11898.3</v>
+        <v>6593.22</v>
       </c>
       <c r="J57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K57">
         <v>0</v>
@@ -4364,16 +4388,16 @@
         <v>0</v>
       </c>
       <c r="M57" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N57">
         <v>33</v>
       </c>
       <c r="O57" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P57" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4381,28 +4405,28 @@
         <v>72</v>
       </c>
       <c r="B58" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C58" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D58" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E58" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="F58" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I58">
-        <v>4151.69</v>
+        <v>11898.3</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K58">
         <v>0</v>
@@ -4411,16 +4435,16 @@
         <v>0</v>
       </c>
       <c r="M58" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N58">
         <v>33</v>
       </c>
       <c r="O58" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P58" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4428,46 +4452,46 @@
         <v>73</v>
       </c>
       <c r="B59" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C59" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D59" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E59" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F59" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="H59">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>40304.19</v>
+        <v>4151.69</v>
       </c>
       <c r="J59">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="K59">
         <v>0</v>
       </c>
       <c r="L59">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M59" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N59">
         <v>33</v>
       </c>
       <c r="O59" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P59" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4475,46 +4499,46 @@
         <v>74</v>
       </c>
       <c r="B60" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C60" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D60" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E60" t="s">
         <v>377</v>
       </c>
       <c r="F60" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="H60">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="I60">
-        <v>230668.57</v>
+        <v>47349.06</v>
       </c>
       <c r="J60">
-        <v>32</v>
+        <v>125</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M60" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N60">
         <v>33</v>
       </c>
       <c r="O60" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P60" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4522,46 +4546,46 @@
         <v>75</v>
       </c>
       <c r="B61" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C61" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D61" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E61" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="F61" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="H61">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="I61">
-        <v>19060.2</v>
+        <v>309896.51</v>
       </c>
       <c r="J61">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="K61">
         <v>0</v>
       </c>
       <c r="L61">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M61" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N61">
         <v>33</v>
       </c>
       <c r="O61" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P61" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4569,46 +4593,46 @@
         <v>76</v>
       </c>
       <c r="B62" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C62" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D62" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E62" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="F62" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H62">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="I62">
-        <v>30579.64</v>
+        <v>19060.2</v>
       </c>
       <c r="J62">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="K62">
         <v>0</v>
       </c>
       <c r="L62">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M62" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N62">
         <v>33</v>
       </c>
       <c r="O62" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P62" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4616,46 +4640,46 @@
         <v>77</v>
       </c>
       <c r="B63" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C63" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D63" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E63" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F63" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="H63">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="I63">
-        <v>134377.9</v>
+        <v>37484.72</v>
       </c>
       <c r="J63">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M63" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N63">
         <v>33</v>
       </c>
       <c r="O63" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P63" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4663,46 +4687,46 @@
         <v>78</v>
       </c>
       <c r="B64" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C64" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D64" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E64" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F64" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="H64">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="I64">
-        <v>18503.4</v>
+        <v>159991.42</v>
       </c>
       <c r="J64">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M64" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N64">
         <v>33</v>
       </c>
       <c r="O64" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P64" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4710,28 +4734,28 @@
         <v>79</v>
       </c>
       <c r="B65" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C65" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D65" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E65" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F65" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I65">
-        <v>3770.34</v>
+        <v>21587.3</v>
       </c>
       <c r="J65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -4740,16 +4764,16 @@
         <v>0</v>
       </c>
       <c r="M65" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N65">
         <v>33</v>
       </c>
       <c r="O65" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P65" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4757,25 +4781,25 @@
         <v>80</v>
       </c>
       <c r="B66" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C66" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D66" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E66" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F66" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="H66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I66">
-        <v>32201.7</v>
+        <v>3770.34</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -4787,16 +4811,16 @@
         <v>0</v>
       </c>
       <c r="M66" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N66">
         <v>33</v>
       </c>
       <c r="O66" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P66" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4804,28 +4828,28 @@
         <v>81</v>
       </c>
       <c r="B67" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C67" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D67" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E67" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F67" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I67">
-        <v>0</v>
+        <v>32201.7</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -4834,16 +4858,16 @@
         <v>0</v>
       </c>
       <c r="M67" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N67">
         <v>33</v>
       </c>
       <c r="O67" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P67" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4851,28 +4875,28 @@
         <v>82</v>
       </c>
       <c r="B68" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C68" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D68" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E68" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F68" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="H68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68">
-        <v>10922.88</v>
+        <v>0</v>
       </c>
       <c r="J68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -4881,16 +4905,16 @@
         <v>0</v>
       </c>
       <c r="M68" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N68">
         <v>33</v>
       </c>
       <c r="O68" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P68" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4898,28 +4922,28 @@
         <v>83</v>
       </c>
       <c r="B69" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C69" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D69" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E69" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F69" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I69">
-        <v>8664.4</v>
+        <v>10922.88</v>
       </c>
       <c r="J69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K69">
         <v>0</v>
@@ -4928,16 +4952,16 @@
         <v>0</v>
       </c>
       <c r="M69" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N69">
         <v>33</v>
       </c>
       <c r="O69" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P69" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4945,46 +4969,46 @@
         <v>84</v>
       </c>
       <c r="B70" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C70" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D70" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E70" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F70" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>8664.4</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M70" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N70">
         <v>33</v>
       </c>
       <c r="O70" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P70" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4992,46 +5016,46 @@
         <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C71" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D71" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E71" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F71" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="H71">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I71">
-        <v>118169.28</v>
+        <v>0</v>
       </c>
       <c r="J71">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M71" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N71">
         <v>33</v>
       </c>
       <c r="O71" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P71" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5039,46 +5063,46 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C72" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D72" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E72" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F72" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>132940.44</v>
       </c>
       <c r="J72">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M72" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N72">
         <v>33</v>
       </c>
       <c r="O72" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P72" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5086,28 +5110,28 @@
         <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C73" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D73" t="s">
-        <v>282</v>
+        <v>328</v>
       </c>
       <c r="E73" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="F73" t="s">
-        <v>386</v>
+        <v>418</v>
       </c>
       <c r="H73">
         <v>1</v>
       </c>
       <c r="I73">
-        <v>1312.71</v>
+        <v>7626.27</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73">
         <v>0</v>
@@ -5116,16 +5140,16 @@
         <v>0</v>
       </c>
       <c r="M73" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N73">
         <v>33</v>
       </c>
       <c r="O73" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P73" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5133,25 +5157,25 @@
         <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C74" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D74" t="s">
-        <v>286</v>
+        <v>329</v>
       </c>
       <c r="E74" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="F74" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="H74">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I74">
-        <v>-1863.56</v>
+        <v>0</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -5163,16 +5187,16 @@
         <v>0</v>
       </c>
       <c r="M74" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N74">
         <v>33</v>
       </c>
       <c r="O74" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P74" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5180,46 +5204,46 @@
         <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C75" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D75" t="s">
-        <v>324</v>
+        <v>287</v>
       </c>
       <c r="E75" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="F75" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="H75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I75">
-        <v>36606.77</v>
+        <v>1312.71</v>
       </c>
       <c r="J75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K75">
         <v>0</v>
       </c>
       <c r="L75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N75">
         <v>33</v>
       </c>
       <c r="O75" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P75" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5227,25 +5251,25 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C76" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D76" t="s">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="E76" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F76" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I76">
-        <v>0</v>
+        <v>-1863.56</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -5257,16 +5281,16 @@
         <v>0</v>
       </c>
       <c r="M76" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N76">
         <v>33</v>
       </c>
       <c r="O76" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P76" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5274,46 +5298,46 @@
         <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C77" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D77" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E77" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F77" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I77">
-        <v>0</v>
+        <v>36606.77</v>
       </c>
       <c r="J77">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K77">
         <v>0</v>
       </c>
       <c r="L77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N77">
         <v>33</v>
       </c>
       <c r="O77" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P77" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5321,25 +5345,25 @@
         <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C78" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D78" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E78" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F78" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78">
-        <v>1609.32</v>
+        <v>0</v>
       </c>
       <c r="J78">
         <v>1</v>
@@ -5351,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="M78" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N78">
         <v>33</v>
       </c>
       <c r="O78" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P78" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5368,25 +5392,25 @@
         <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C79" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D79" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E79" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="F79" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="H79">
         <v>1</v>
       </c>
       <c r="I79">
-        <v>2524.58</v>
+        <v>3551.07</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -5398,16 +5422,16 @@
         <v>0</v>
       </c>
       <c r="M79" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N79">
         <v>33</v>
       </c>
       <c r="O79" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P79" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5415,46 +5439,46 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C80" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D80" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E80" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F80" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="H80">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I80">
-        <v>11291.52</v>
+        <v>1609.32</v>
       </c>
       <c r="J80">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K80">
         <v>0</v>
       </c>
       <c r="L80">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M80" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N80">
         <v>33</v>
       </c>
       <c r="O80" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P80" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5462,28 +5486,28 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C81" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D81" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E81" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F81" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="H81">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I81">
-        <v>9645.780000000001</v>
+        <v>7573.74</v>
       </c>
       <c r="J81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K81">
         <v>0</v>
@@ -5492,16 +5516,16 @@
         <v>0</v>
       </c>
       <c r="M81" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N81">
         <v>33</v>
       </c>
       <c r="O81" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P81" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5509,46 +5533,46 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C82" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D82" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E82" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F82" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="H82">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I82">
-        <v>19978.72</v>
+        <v>12898.3</v>
       </c>
       <c r="J82">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K82">
         <v>0</v>
       </c>
       <c r="L82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M82" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N82">
         <v>33</v>
       </c>
       <c r="O82" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P82" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5556,46 +5580,46 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C83" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D83" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E83" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F83" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="H83">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="I83">
-        <v>80669.21000000001</v>
+        <v>9645.780000000001</v>
       </c>
       <c r="J83">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="K83">
         <v>0</v>
       </c>
       <c r="L83">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M83" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N83">
         <v>33</v>
       </c>
       <c r="O83" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P83" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5603,46 +5627,46 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C84" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D84" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E84" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="F84" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="H84">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="I84">
-        <v>1444.08</v>
+        <v>26927.84</v>
       </c>
       <c r="J84">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="K84">
         <v>0</v>
       </c>
       <c r="L84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M84" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N84">
         <v>33</v>
       </c>
       <c r="O84" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P84" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5650,46 +5674,46 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C85" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D85" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E85" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F85" t="s">
-        <v>414</v>
+        <v>385</v>
       </c>
       <c r="H85">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="I85">
-        <v>40029.64</v>
+        <v>85343.77</v>
       </c>
       <c r="J85">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="K85">
         <v>0</v>
       </c>
       <c r="L85">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M85" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N85">
         <v>33</v>
       </c>
       <c r="O85" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P85" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5697,46 +5721,46 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C86" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D86" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E86" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F86" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I86">
-        <v>0</v>
+        <v>1444.08</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K86">
         <v>0</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M86" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N86">
         <v>33</v>
       </c>
       <c r="O86" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P86" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5744,46 +5768,46 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C87" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D87" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E87" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F87" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="H87">
+        <v>12</v>
+      </c>
+      <c r="I87">
+        <v>96071.14999999999</v>
+      </c>
+      <c r="J87">
+        <v>8</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
         <v>1</v>
       </c>
-      <c r="I87">
-        <v>4914.41</v>
-      </c>
-      <c r="J87">
-        <v>1</v>
-      </c>
-      <c r="K87">
-        <v>0</v>
-      </c>
-      <c r="L87">
-        <v>0</v>
-      </c>
       <c r="M87" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N87">
         <v>33</v>
       </c>
       <c r="O87" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P87" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5791,25 +5815,25 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C88" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D88" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E88" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F88" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="H88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88">
-        <v>3507.63</v>
+        <v>0</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5821,16 +5845,16 @@
         <v>0</v>
       </c>
       <c r="M88" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N88">
         <v>33</v>
       </c>
       <c r="O88" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P88" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5838,25 +5862,25 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C89" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D89" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E89" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F89" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="H89">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I89">
-        <v>-9321.190000000001</v>
+        <v>4914.41</v>
       </c>
       <c r="J89">
         <v>1</v>
@@ -5865,19 +5889,19 @@
         <v>0</v>
       </c>
       <c r="L89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N89">
         <v>33</v>
       </c>
       <c r="O89" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P89" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5885,28 +5909,28 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C90" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D90" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="E90" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="F90" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I90">
-        <v>0</v>
+        <v>7015.25</v>
       </c>
       <c r="J90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90">
         <v>0</v>
@@ -5915,16 +5939,16 @@
         <v>0</v>
       </c>
       <c r="M90" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N90">
         <v>33</v>
       </c>
       <c r="O90" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P90" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5932,46 +5956,46 @@
         <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C91" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D91" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="E91" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="F91" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I91">
-        <v>0</v>
+        <v>-9321.190000000001</v>
       </c>
       <c r="J91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K91">
         <v>0</v>
       </c>
       <c r="L91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N91">
         <v>33</v>
       </c>
       <c r="O91" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P91" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5979,46 +6003,46 @@
         <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C92" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D92" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E92" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="F92" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="H92">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="I92">
-        <v>80198.64</v>
+        <v>0</v>
       </c>
       <c r="J92">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="K92">
         <v>0</v>
       </c>
       <c r="L92">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M92" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N92">
         <v>33</v>
       </c>
       <c r="O92" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P92" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6026,46 +6050,46 @@
         <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C93" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D93" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="E93" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="F93" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="H93">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I93">
-        <v>7622.9</v>
+        <v>0</v>
       </c>
       <c r="J93">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K93">
         <v>0</v>
       </c>
       <c r="L93">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M93" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N93">
         <v>33</v>
       </c>
       <c r="O93" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P93" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6073,46 +6097,46 @@
         <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C94" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D94" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E94" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="F94" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="H94">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="I94">
-        <v>19149.16</v>
+        <v>96031.75999999999</v>
       </c>
       <c r="J94">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="K94">
         <v>0</v>
       </c>
       <c r="L94">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M94" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N94">
         <v>33</v>
       </c>
       <c r="O94" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P94" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6120,28 +6144,28 @@
         <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C95" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D95" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E95" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="F95" t="s">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="H95">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I95">
-        <v>0</v>
+        <v>9147.48</v>
       </c>
       <c r="J95">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K95">
         <v>0</v>
@@ -6150,16 +6174,16 @@
         <v>9</v>
       </c>
       <c r="M95" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N95">
         <v>33</v>
       </c>
       <c r="O95" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P95" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6167,46 +6191,46 @@
         <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C96" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D96" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E96" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="F96" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="H96">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I96">
-        <v>11433.06</v>
+        <v>19149.16</v>
       </c>
       <c r="J96">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K96">
         <v>0</v>
       </c>
       <c r="L96">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M96" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N96">
         <v>33</v>
       </c>
       <c r="O96" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P96" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6214,46 +6238,46 @@
         <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C97" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D97" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E97" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F97" t="s">
-        <v>368</v>
+        <v>407</v>
       </c>
       <c r="H97">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I97">
-        <v>12707.65</v>
+        <v>0</v>
       </c>
       <c r="J97">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K97">
         <v>0</v>
       </c>
       <c r="L97">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M97" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N97">
         <v>33</v>
       </c>
       <c r="O97" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P97" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6261,46 +6285,46 @@
         <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C98" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D98" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E98" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="F98" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I98">
-        <v>0</v>
+        <v>13973.74</v>
       </c>
       <c r="J98">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K98">
         <v>0</v>
       </c>
       <c r="L98">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M98" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N98">
         <v>33</v>
       </c>
       <c r="O98" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P98" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6308,46 +6332,46 @@
         <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C99" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D99" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E99" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="F99" t="s">
-        <v>423</v>
+        <v>374</v>
       </c>
       <c r="H99">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="I99">
-        <v>152023.78</v>
+        <v>17790.71</v>
       </c>
       <c r="J99">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="K99">
         <v>0</v>
       </c>
       <c r="L99">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M99" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N99">
         <v>33</v>
       </c>
       <c r="O99" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P99" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6355,46 +6379,46 @@
         <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C100" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D100" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E100" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F100" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="H100">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I100">
-        <v>75329.67</v>
+        <v>0</v>
       </c>
       <c r="J100">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K100">
         <v>0</v>
       </c>
       <c r="L100">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M100" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N100">
         <v>33</v>
       </c>
       <c r="O100" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P100" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6402,46 +6426,46 @@
         <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C101" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D101" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E101" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F101" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="H101">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="I101">
-        <v>16945.76</v>
+        <v>178840.74</v>
       </c>
       <c r="J101">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="K101">
         <v>0</v>
       </c>
       <c r="L101">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M101" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N101">
         <v>33</v>
       </c>
       <c r="O101" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P101" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6449,25 +6473,25 @@
         <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C102" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D102" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E102" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F102" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="H102">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I102">
-        <v>85994.03</v>
+        <v>125409.33</v>
       </c>
       <c r="J102">
         <v>15</v>
@@ -6476,19 +6500,19 @@
         <v>0</v>
       </c>
       <c r="L102">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M102" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N102">
         <v>33</v>
       </c>
       <c r="O102" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P102" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6496,28 +6520,28 @@
         <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C103" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D103" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E103" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F103" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="H103">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I103">
-        <v>6679.66</v>
+        <v>16945.76</v>
       </c>
       <c r="J103">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K103">
         <v>0</v>
@@ -6526,16 +6550,16 @@
         <v>0</v>
       </c>
       <c r="M103" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N103">
         <v>33</v>
       </c>
       <c r="O103" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P103" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6543,46 +6567,46 @@
         <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C104" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D104" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E104" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F104" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="H104">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I104">
-        <v>153573.76</v>
+        <v>96110.97</v>
       </c>
       <c r="J104">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K104">
         <v>0</v>
       </c>
       <c r="L104">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M104" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N104">
         <v>33</v>
       </c>
       <c r="O104" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P104" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6590,46 +6614,46 @@
         <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C105" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D105" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="E105" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="F105" t="s">
-        <v>400</v>
+        <v>434</v>
       </c>
       <c r="H105">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I105">
-        <v>10166.11</v>
+        <v>6679.66</v>
       </c>
       <c r="J105">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K105">
         <v>0</v>
       </c>
       <c r="L105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M105" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N105">
         <v>33</v>
       </c>
       <c r="O105" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P105" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6637,46 +6661,46 @@
         <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C106" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D106" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E106" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F106" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="H106">
+        <v>24</v>
+      </c>
+      <c r="I106">
+        <v>160250.88</v>
+      </c>
+      <c r="J106">
+        <v>22</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
         <v>3</v>
       </c>
-      <c r="I106">
-        <v>21607.62</v>
-      </c>
-      <c r="J106">
-        <v>2</v>
-      </c>
-      <c r="K106">
-        <v>0</v>
-      </c>
-      <c r="L106">
-        <v>0</v>
-      </c>
       <c r="M106" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N106">
         <v>33</v>
       </c>
       <c r="O106" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P106" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6684,46 +6708,46 @@
         <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C107" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D107" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="E107" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="F107" t="s">
-        <v>428</v>
+        <v>407</v>
       </c>
       <c r="H107">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I107">
-        <v>20076.25</v>
+        <v>10166.11</v>
       </c>
       <c r="J107">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K107">
         <v>0</v>
       </c>
       <c r="L107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N107">
         <v>33</v>
       </c>
       <c r="O107" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P107" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6731,28 +6755,28 @@
         <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C108" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D108" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E108" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F108" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="H108">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I108">
-        <v>14826.25</v>
+        <v>28810.16</v>
       </c>
       <c r="J108">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K108">
         <v>0</v>
@@ -6761,16 +6785,16 @@
         <v>0</v>
       </c>
       <c r="M108" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N108">
         <v>33</v>
       </c>
       <c r="O108" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P108" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6778,46 +6802,46 @@
         <v>123</v>
       </c>
       <c r="B109" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C109" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D109" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E109" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="F109" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="H109">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I109">
-        <v>8844.059999999999</v>
+        <v>20076.25</v>
       </c>
       <c r="J109">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K109">
         <v>0</v>
       </c>
       <c r="L109">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M109" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N109">
         <v>33</v>
       </c>
       <c r="O109" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P109" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6825,46 +6849,46 @@
         <v>124</v>
       </c>
       <c r="B110" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C110" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D110" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E110" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="F110" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="H110">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I110">
-        <v>5591.52</v>
+        <v>17791.51</v>
       </c>
       <c r="J110">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K110">
         <v>0</v>
       </c>
       <c r="L110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N110">
         <v>33</v>
       </c>
       <c r="O110" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P110" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6872,46 +6896,46 @@
         <v>125</v>
       </c>
       <c r="B111" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C111" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D111" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E111" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="F111" t="s">
-        <v>402</v>
+        <v>438</v>
       </c>
       <c r="H111">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="I111">
-        <v>284705.28</v>
+        <v>8844.059999999999</v>
       </c>
       <c r="J111">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="K111">
         <v>0</v>
       </c>
       <c r="L111">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="M111" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N111">
         <v>33</v>
       </c>
       <c r="O111" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P111" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6919,46 +6943,46 @@
         <v>126</v>
       </c>
       <c r="B112" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C112" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D112" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E112" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="F112" t="s">
-        <v>391</v>
+        <v>439</v>
       </c>
       <c r="H112">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I112">
-        <v>2877.97</v>
+        <v>5591.52</v>
       </c>
       <c r="J112">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K112">
         <v>0</v>
       </c>
       <c r="L112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N112">
         <v>33</v>
       </c>
       <c r="O112" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P112" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6966,46 +6990,46 @@
         <v>127</v>
       </c>
       <c r="B113" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C113" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D113" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E113" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="F113" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="H113">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="I113">
-        <v>2158.47</v>
+        <v>355881.6</v>
       </c>
       <c r="J113">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="K113">
         <v>0</v>
       </c>
       <c r="L113">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M113" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N113">
         <v>33</v>
       </c>
       <c r="O113" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P113" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7013,28 +7037,28 @@
         <v>128</v>
       </c>
       <c r="B114" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C114" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D114" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E114" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="F114" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H114">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I114">
-        <v>1270.34</v>
+        <v>2877.97</v>
       </c>
       <c r="J114">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K114">
         <v>0</v>
@@ -7043,16 +7067,16 @@
         <v>0</v>
       </c>
       <c r="M114" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N114">
         <v>33</v>
       </c>
       <c r="O114" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P114" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7060,46 +7084,46 @@
         <v>129</v>
       </c>
       <c r="B115" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C115" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D115" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E115" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F115" t="s">
-        <v>432</v>
+        <v>397</v>
       </c>
       <c r="H115">
         <v>3</v>
       </c>
       <c r="I115">
-        <v>19065.24</v>
+        <v>2158.47</v>
       </c>
       <c r="J115">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K115">
         <v>0</v>
       </c>
       <c r="L115">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M115" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N115">
         <v>33</v>
       </c>
       <c r="O115" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P115" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7107,25 +7131,25 @@
         <v>130</v>
       </c>
       <c r="B116" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C116" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D116" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E116" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F116" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="H116">
         <v>1</v>
       </c>
       <c r="I116">
-        <v>4236.44</v>
+        <v>1270.34</v>
       </c>
       <c r="J116">
         <v>1</v>
@@ -7137,16 +7161,16 @@
         <v>0</v>
       </c>
       <c r="M116" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N116">
         <v>33</v>
       </c>
       <c r="O116" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P116" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7154,46 +7178,46 @@
         <v>131</v>
       </c>
       <c r="B117" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C117" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D117" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E117" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="F117" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="H117">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I117">
-        <v>7624.58</v>
+        <v>25420.32</v>
       </c>
       <c r="J117">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K117">
         <v>0</v>
       </c>
       <c r="L117">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M117" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N117">
         <v>33</v>
       </c>
       <c r="O117" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P117" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7201,46 +7225,46 @@
         <v>132</v>
       </c>
       <c r="B118" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C118" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D118" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E118" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="F118" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="H118">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I118">
-        <v>61022.04</v>
+        <v>4236.44</v>
       </c>
       <c r="J118">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K118">
         <v>0</v>
       </c>
       <c r="L118">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M118" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N118">
         <v>33</v>
       </c>
       <c r="O118" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="P118" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7248,46 +7272,140 @@
         <v>133</v>
       </c>
       <c r="B119" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C119" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D119" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E119" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="F119" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="H119">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I119">
-        <v>90155.97</v>
+        <v>7624.58</v>
       </c>
       <c r="J119">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K119">
         <v>0</v>
       </c>
       <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119" t="s">
+        <v>445</v>
+      </c>
+      <c r="N119">
+        <v>33</v>
+      </c>
+      <c r="O119" t="s">
+        <v>446</v>
+      </c>
+      <c r="P119" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16">
+      <c r="A120" t="s">
+        <v>134</v>
+      </c>
+      <c r="B120" t="s">
+        <v>254</v>
+      </c>
+      <c r="C120" t="s">
+        <v>256</v>
+      </c>
+      <c r="D120" t="s">
+        <v>371</v>
+      </c>
+      <c r="E120" t="s">
+        <v>389</v>
+      </c>
+      <c r="F120" t="s">
+        <v>443</v>
+      </c>
+      <c r="H120">
+        <v>20</v>
+      </c>
+      <c r="I120">
+        <v>61022.04</v>
+      </c>
+      <c r="J120">
+        <v>20</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>4</v>
+      </c>
+      <c r="M120" t="s">
+        <v>445</v>
+      </c>
+      <c r="N120">
+        <v>33</v>
+      </c>
+      <c r="O120" t="s">
+        <v>446</v>
+      </c>
+      <c r="P120" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16">
+      <c r="A121" t="s">
+        <v>135</v>
+      </c>
+      <c r="B121" t="s">
+        <v>255</v>
+      </c>
+      <c r="C121" t="s">
+        <v>256</v>
+      </c>
+      <c r="D121" t="s">
+        <v>372</v>
+      </c>
+      <c r="E121" t="s">
+        <v>389</v>
+      </c>
+      <c r="F121" t="s">
+        <v>444</v>
+      </c>
+      <c r="H121">
+        <v>19</v>
+      </c>
+      <c r="I121">
+        <v>107060.22</v>
+      </c>
+      <c r="J121">
+        <v>17</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
         <v>8</v>
       </c>
-      <c r="M119" t="s">
-        <v>437</v>
-      </c>
-      <c r="N119">
-        <v>33</v>
-      </c>
-      <c r="O119" t="s">
-        <v>438</v>
-      </c>
-      <c r="P119" t="s">
-        <v>439</v>
+      <c r="M121" t="s">
+        <v>445</v>
+      </c>
+      <c r="N121">
+        <v>33</v>
+      </c>
+      <c r="O121" t="s">
+        <v>446</v>
+      </c>
+      <c r="P121" t="s">
+        <v>447</v>
       </c>
     </row>
   </sheetData>
